--- a/ideas.xlsx
+++ b/ideas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM51"/>
+  <dimension ref="A1:AP121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,140 +486,155 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>qwen3_32b_novelty</t>
+          <t>qwen_feasibility</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>qwen3_32b_feasibility</t>
+          <t>qwen_impact</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>qwen3_32b_impact</t>
+          <t>qwen_presentation</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>qwen3_32b_presentation</t>
+          <t>qwen_overall</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>qwen3_32b_overall</t>
+          <t>qwen_rank</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>qwen3_32b_rank</t>
+          <t>mistral_feasibility</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>qwen3_32b_feedback</t>
+          <t>mistral_impact</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>deepseek_novelty</t>
+          <t>mistral_presentation</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>deepseek_feasibility</t>
+          <t>mistral_overall</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>deepseek_impact</t>
+          <t>mistral_rank</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>deepseek_presentation</t>
+          <t>llama_novelty</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>deepseek_overall</t>
+          <t>llama_feasibility</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>deepseek_rank</t>
+          <t>llama_impact</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>deepseek_feedback</t>
+          <t>llama_presentation</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>llama_novelty</t>
+          <t>llama_overall</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>llama_feasibility</t>
+          <t>llama_rank</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>llama_impact</t>
+          <t>llama_feedback</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>llama_presentation</t>
+          <t>llama_status</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>llama_overall</t>
+          <t>mistral_status</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>llama_rank</t>
+          <t>qwen_status</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>llama_feedback</t>
+          <t>avg_overall</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>avg_overall</t>
+          <t>final_rank</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>final_rank</t>
+          <t>ai_advance</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>ai_advance</t>
+          <t>agrees_with_expert</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>agrees_with_expert</t>
+          <t>llama_accuracy</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>pairwise_wins</t>
+          <t>mistral_accuracy</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>pairwise_rank</t>
+          <t>qwen_accuracy</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>combined_accuracy</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>score_spread</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>human_review_required</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>spearman_rank_correlation</t>
         </is>
@@ -695,6 +710,9 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -766,6 +784,9 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -837,6 +858,9 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -908,6 +932,9 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -979,6 +1006,9 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1050,6 +1080,9 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1121,6 +1154,9 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1192,6 +1228,9 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1263,6 +1302,9 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1334,6 +1376,9 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1363,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1405,6 +1450,9 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1434,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1476,6 +1524,9 @@
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1505,16 +1556,16 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1547,6 +1598,9 @@
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1576,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -1585,7 +1639,7 @@
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1618,6 +1672,9 @@
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1647,16 +1704,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1689,6 +1746,9 @@
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1760,6 +1820,9 @@
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1831,6 +1894,9 @@
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1902,6 +1968,9 @@
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1973,6 +2042,9 @@
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2044,6 +2116,9 @@
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2115,6 +2190,9 @@
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2186,6 +2264,9 @@
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2257,6 +2338,9 @@
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2328,6 +2412,9 @@
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2399,6 +2486,9 @@
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2428,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
@@ -2470,6 +2560,9 @@
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2541,6 +2634,9 @@
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2570,16 +2666,16 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2612,6 +2708,9 @@
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2641,16 +2740,16 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2683,6 +2782,9 @@
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2754,6 +2856,9 @@
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2825,6 +2930,9 @@
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2896,6 +3004,9 @@
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2925,16 +3036,16 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2967,6 +3078,9 @@
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3038,6 +3152,9 @@
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3109,6 +3226,9 @@
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3138,16 +3258,16 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3180,6 +3300,9 @@
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3251,6 +3374,9 @@
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3322,6 +3448,9 @@
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3393,6 +3522,9 @@
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3464,6 +3596,9 @@
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3493,13 +3628,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
         <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>3</v>
@@ -3535,6 +3670,9 @@
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3564,16 +3702,16 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3606,6 +3744,9 @@
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3677,6 +3818,9 @@
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3748,6 +3892,9 @@
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3777,16 +3924,16 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
         <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -3819,6 +3966,9 @@
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3848,16 +3998,16 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
         <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -3890,6 +4040,9 @@
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3961,6 +4114,9 @@
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3990,13 +4146,13 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -4032,6 +4188,9 @@
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4061,16 +4220,16 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -4103,6 +4262,9 @@
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4174,6 +4336,5189 @@
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HealthTwin Guardian AI</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>An AI health companion that combines medicine recognition, multilingual health guidance, and preventive-care reminders to help users understand everyday health information.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RASIP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>A resilient autonomous drone-swarm platform for civilian disaster response, search and rescue, environmental monitoring, and infrastructure inspection.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Disaster Management</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Guidely</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>An AI indoor-navigation assistant that helps people navigate large buildings such as hospitals, campuses, and shopping centres where conventional GPS is unreliable.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cognure</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>An AI health-memory system that converts scattered medical documents into a searchable health graph and lets users ask questions about their records.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AccessAI</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>An accessibility assistant that converts images and documents into simplified text, summaries, translations, and spoken output directly in the browser.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TerraAI</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>An AI farming copilot that helps farmers identify crop problems and make data-driven decisions for more efficient precision agriculture.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EcoVision</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>An AI-powered environmental app that lets communities report litter and environmental issues, coordinate clean-up activities, and learn about local sustainability problems.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MediXR Trainer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>An immersive medical-training platform using XR, 3D models, and AI guidance to teach healthcare students how to perform clinical procedures safely.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Aegis Consent Companion</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>A multilingual AI assistant that helps patients understand medical consent information in simpler language before discussing procedures with healthcare professionals.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4</v>
+      </c>
+      <c r="J60" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Medical Desert Planner</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>A health-planning platform that combines evidence about healthcare facilities and geography to identify underserved areas and reveal gaps in access to essential care.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>RecycleVision</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Computer-vision app that identifies common household recyclable materials from camera images and explains the correct disposal method.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>3</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>StudySummarizer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AI tool that converts uploaded lecture PDFs into short summaries, key terms, and revision points for students.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ClinicQueue</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>A digital token system that allows patients to join clinic queues remotely and receive notifications when their appointment is approaching.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FoodWaste Tracker</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Mobile app that records household food waste and provides weekly charts and suggestions for reducing unnecessary purchases.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TutorMatch</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Platform matching students with peer tutors based on subject, availability, and preferred learning mode.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>4</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>WaterSaver</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Smart-home dashboard that estimates household water consumption and sends reminders when usage exceeds a user-defined target.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RoadDamage AI</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Phone-camera system that detects potholes and road cracks from images and places them on a map for maintenance teams.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Smart City</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ElderCare Connect</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Simple family dashboard for tracking an elderly relative's appointments, reminders, and routine check-ins.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>InvoiceReader</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OCR-based web tool that extracts invoice numbers, dates, taxes, and totals from uploaded business invoices.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>4</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CampusGuide</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Interactive campus map that helps new students locate classrooms, laboratories, offices, and facilities.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>4</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AirAware</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Mobile dashboard that displays local air-quality readings and gives basic recommendations for outdoor activities.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ResumeLens</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AI resume checker that identifies missing sections, common formatting problems, and keywords that may improve job-search visibility.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>InterviewCoach</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Chatbot that asks mock interview questions and gives basic feedback on answers and communication.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" t="n">
+        <v>4</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ScholarshipFinder</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Search platform that filters scholarship opportunities by course, eligibility, location, and deadline.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MealPlanner AI</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AI meal-planning assistant that creates weekly meal suggestions from dietary preferences and a selected grocery budget.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PhishGuard</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Browser extension that highlights suspicious links and common phishing indicators in webpages and emails.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PasswordCoach</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Security utility that checks password strength and teaches users safer password and authentication practices.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SecureShare</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Web application for sharing files through password-protected links with automatic expiration.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" t="n">
+        <v>2</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PillChecker</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Image-based tool that identifies common medicine packaging and displays basic medicine information from a reference database.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HospitalMap</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Indoor map that guides visitors to departments, laboratories, pharmacies, and waiting areas inside hospitals.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SignBoard Reader</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Mobile accessibility tool that reads photographed public signboards aloud and optionally translates the detected text.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" t="n">
+        <v>4</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CaptionLive</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Speech-to-text application that displays live captions during classroom discussions and small meetings.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" t="n">
+        <v>3</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr"/>
+      <c r="AO83" t="inlineStr"/>
+      <c r="AP83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GestureRemote</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Computer-vision interface that recognizes a small set of hand gestures to control media playback and presentations.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="inlineStr"/>
+      <c r="AP84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>FarmMarket</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Marketplace that lets farmers list produce and allows nearby buyers to compare prices and contact sellers directly.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3</v>
+      </c>
+      <c r="I85" t="n">
+        <v>3</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr"/>
+      <c r="AL85" t="inlineStr"/>
+      <c r="AM85" t="inlineStr"/>
+      <c r="AN85" t="inlineStr"/>
+      <c r="AO85" t="inlineStr"/>
+      <c r="AP85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CropPrice Alert</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Dashboard that displays crop market prices and sends alerts when selected commodities reach a target price.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
+      <c r="AP86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PestLens</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Mobile image classifier that identifies a limited set of common crop pests from photographs and provides basic prevention information.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr"/>
+      <c r="AP87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>IrrigationPlanner</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Simple farm dashboard that combines crop type, soil moisture, and weather information to suggest irrigation schedules.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr"/>
+      <c r="AO88" t="inlineStr"/>
+      <c r="AP88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HarvestLog</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Digital record system for farmers to track planting dates, harvest quantities, fertilizer use, and field notes.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>4</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr"/>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr"/>
+      <c r="AN89" t="inlineStr"/>
+      <c r="AO89" t="inlineStr"/>
+      <c r="AP89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SolarMonitor</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Dashboard for household solar installations showing estimated generation, daily output, and basic performance alerts.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="inlineStr"/>
+      <c r="AP90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EnergySaver</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Home energy dashboard that tracks appliance usage and provides simple suggestions for reducing electricity consumption.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3</v>
+      </c>
+      <c r="I91" t="n">
+        <v>3</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr"/>
+      <c r="AK91" t="inlineStr"/>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="inlineStr"/>
+      <c r="AN91" t="inlineStr"/>
+      <c r="AO91" t="inlineStr"/>
+      <c r="AP91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EVCharge Finder</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mobile app showing nearby electric-vehicle charging stations with availability, distance, and basic navigation.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>4</v>
+      </c>
+      <c r="I92" t="n">
+        <v>2</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="inlineStr"/>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr"/>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr"/>
+      <c r="AO92" t="inlineStr"/>
+      <c r="AP92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CarpoolConnect</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Community platform matching commuters travelling along similar routes so they can coordinate shared rides.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3</v>
+      </c>
+      <c r="I93" t="n">
+        <v>2</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr"/>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr"/>
+      <c r="AO93" t="inlineStr"/>
+      <c r="AP93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ParkingPredict</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Prediction dashboard estimating parking availability around selected locations using historical occupancy patterns.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" t="n">
+        <v>2</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr"/>
+      <c r="AL94" t="inlineStr"/>
+      <c r="AM94" t="inlineStr"/>
+      <c r="AN94" t="inlineStr"/>
+      <c r="AO94" t="inlineStr"/>
+      <c r="AP94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MetroMate</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Public-transport assistant that combines route information and estimated travel time to suggest convenient metro connections.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr"/>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr"/>
+      <c r="AL95" t="inlineStr"/>
+      <c r="AM95" t="inlineStr"/>
+      <c r="AN95" t="inlineStr"/>
+      <c r="AO95" t="inlineStr"/>
+      <c r="AP95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>DisasterConnect</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Emergency coordination portal where residents can report needs and volunteers can offer food, transport, or temporary shelter.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Disaster Management</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>3</v>
+      </c>
+      <c r="I96" t="n">
+        <v>3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr"/>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="inlineStr"/>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr"/>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="inlineStr"/>
+      <c r="AN96" t="inlineStr"/>
+      <c r="AO96" t="inlineStr"/>
+      <c r="AP96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ReliefInventory</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Dashboard for relief teams to track donated food, medicines, clothing, and distribution quantities during emergencies.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Disaster Management</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="n">
+        <v>4</v>
+      </c>
+      <c r="I97" t="n">
+        <v>3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="inlineStr"/>
+      <c r="AD97" t="inlineStr"/>
+      <c r="AE97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="inlineStr"/>
+      <c r="AN97" t="inlineStr"/>
+      <c r="AO97" t="inlineStr"/>
+      <c r="AP97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>EmergencyTranslate</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Translation assistant that converts short emergency messages between local languages for use during disaster response.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Disaster Management</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>3</v>
+      </c>
+      <c r="I98" t="n">
+        <v>3</v>
+      </c>
+      <c r="J98" t="n">
+        <v>2</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr"/>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98" t="inlineStr"/>
+      <c r="AN98" t="inlineStr"/>
+      <c r="AO98" t="inlineStr"/>
+      <c r="AP98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ShelterFinder</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Map-based application listing nearby emergency shelters and displaying capacity information when available.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Disaster Management</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" t="n">
+        <v>4</v>
+      </c>
+      <c r="I99" t="n">
+        <v>3</v>
+      </c>
+      <c r="J99" t="n">
+        <v>2</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr"/>
+      <c r="AN99" t="inlineStr"/>
+      <c r="AO99" t="inlineStr"/>
+      <c r="AP99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LegalDocCheck</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AI document assistant that highlights dates, parties, obligations, and potentially important clauses in uploaded agreements.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>3</v>
+      </c>
+      <c r="J100" t="n">
+        <v>2</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr"/>
+      <c r="AN100" t="inlineStr"/>
+      <c r="AO100" t="inlineStr"/>
+      <c r="AP100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>TenantHelper</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Information portal that explains common rental-document terms and provides a checklist for tenants before signing an agreement.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>4</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="inlineStr"/>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
+      <c r="AN101" t="inlineStr"/>
+      <c r="AO101" t="inlineStr"/>
+      <c r="AP101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ClaimAssist</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Insurance assistant that extracts basic information from claim documents and creates a checklist of missing fields.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3</v>
+      </c>
+      <c r="I102" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" t="n">
+        <v>2</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr"/>
+      <c r="AO102" t="inlineStr"/>
+      <c r="AP102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>FraudFlagger</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Transaction-monitoring dashboard that flags unusual spending patterns using simple anomaly-detection rules.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3</v>
+      </c>
+      <c r="I103" t="n">
+        <v>3</v>
+      </c>
+      <c r="J103" t="n">
+        <v>2</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr"/>
+      <c r="AO103" t="inlineStr"/>
+      <c r="AP103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BillSplit AI</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Receipt-scanning app that identifies items on a restaurant bill and calculates each person's share.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>4</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" t="n">
+        <v>2</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr"/>
+      <c r="AO104" t="inlineStr"/>
+      <c r="AP104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SavingsCoach</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Personal finance chatbot that suggests simple saving targets from a user's monthly income and spending categories.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>4</v>
+      </c>
+      <c r="I105" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" t="n">
+        <v>2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="inlineStr"/>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="inlineStr"/>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="inlineStr"/>
+      <c r="AN105" t="inlineStr"/>
+      <c r="AO105" t="inlineStr"/>
+      <c r="AP105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NewsVerify</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tool that compares selected news claims with a collection of fact-checking sources and presents matching evidence.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>3</v>
+      </c>
+      <c r="J106" t="n">
+        <v>2</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr"/>
+      <c r="AC106" t="inlineStr"/>
+      <c r="AD106" t="inlineStr"/>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr"/>
+      <c r="AM106" t="inlineStr"/>
+      <c r="AN106" t="inlineStr"/>
+      <c r="AO106" t="inlineStr"/>
+      <c r="AP106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ArticleSimplify</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Browser tool that converts long online articles into shorter summaries and extracts important points.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>4</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="inlineStr"/>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="inlineStr"/>
+      <c r="AN107" t="inlineStr"/>
+      <c r="AO107" t="inlineStr"/>
+      <c r="AP107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Misinformation Coach</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Educational web app that teaches users how to identify common misinformation patterns through interactive examples.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" t="n">
+        <v>4</v>
+      </c>
+      <c r="I108" t="n">
+        <v>3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="inlineStr"/>
+      <c r="AD108" t="inlineStr"/>
+      <c r="AE108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="inlineStr"/>
+      <c r="AN108" t="inlineStr"/>
+      <c r="AO108" t="inlineStr"/>
+      <c r="AP108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CommunityAlert</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Neighbourhood platform for sharing verified local announcements, road closures, public-service notices, and emergency information.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="n">
+        <v>4</v>
+      </c>
+      <c r="I109" t="n">
+        <v>2</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="inlineStr"/>
+      <c r="AK109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="inlineStr"/>
+      <c r="AN109" t="inlineStr"/>
+      <c r="AO109" t="inlineStr"/>
+      <c r="AP109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>VolunteerMatch</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Platform connecting volunteers with nearby community activities based on interests, skills, and available time.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Social Impact</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="n">
+        <v>4</v>
+      </c>
+      <c r="I110" t="n">
+        <v>3</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="inlineStr"/>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
+      <c r="AC110" t="inlineStr"/>
+      <c r="AD110" t="inlineStr"/>
+      <c r="AE110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
+      <c r="AJ110" t="inlineStr"/>
+      <c r="AK110" t="inlineStr"/>
+      <c r="AL110" t="inlineStr"/>
+      <c r="AM110" t="inlineStr"/>
+      <c r="AN110" t="inlineStr"/>
+      <c r="AO110" t="inlineStr"/>
+      <c r="AP110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>DonationTracker</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Simple dashboard for non-profits to record donations, donor information, and distribution activities.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Social Impact</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>4</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2</v>
+      </c>
+      <c r="J111" t="n">
+        <v>2</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr"/>
+      <c r="AC111" t="inlineStr"/>
+      <c r="AD111" t="inlineStr"/>
+      <c r="AE111" t="inlineStr"/>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr"/>
+      <c r="AJ111" t="inlineStr"/>
+      <c r="AK111" t="inlineStr"/>
+      <c r="AL111" t="inlineStr"/>
+      <c r="AM111" t="inlineStr"/>
+      <c r="AN111" t="inlineStr"/>
+      <c r="AO111" t="inlineStr"/>
+      <c r="AP111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>AccessibleForms</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Form-building tool that checks basic accessibility issues such as missing labels, poor contrast, and unclear input instructions.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" t="n">
+        <v>3</v>
+      </c>
+      <c r="I112" t="n">
+        <v>3</v>
+      </c>
+      <c r="J112" t="n">
+        <v>2</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="inlineStr"/>
+      <c r="AK112" t="inlineStr"/>
+      <c r="AL112" t="inlineStr"/>
+      <c r="AM112" t="inlineStr"/>
+      <c r="AN112" t="inlineStr"/>
+      <c r="AO112" t="inlineStr"/>
+      <c r="AP112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ColorAssist</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Browser extension that applies alternative colour palettes to improve readability for users with common colour-vision deficiencies.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="n">
+        <v>4</v>
+      </c>
+      <c r="I113" t="n">
+        <v>2</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="inlineStr"/>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr"/>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="inlineStr"/>
+      <c r="AK113" t="inlineStr"/>
+      <c r="AL113" t="inlineStr"/>
+      <c r="AM113" t="inlineStr"/>
+      <c r="AN113" t="inlineStr"/>
+      <c r="AO113" t="inlineStr"/>
+      <c r="AP113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>VoiceForm</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Voice-enabled form assistant that lets users dictate common fields instead of typing them manually.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="n">
+        <v>4</v>
+      </c>
+      <c r="I114" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" t="n">
+        <v>2</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="inlineStr"/>
+      <c r="AK114" t="inlineStr"/>
+      <c r="AL114" t="inlineStr"/>
+      <c r="AM114" t="inlineStr"/>
+      <c r="AN114" t="inlineStr"/>
+      <c r="AO114" t="inlineStr"/>
+      <c r="AP114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>FocusTimer AI</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Study productivity app that tracks focused sessions and recommends break intervals based on the user's previous sessions.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="n">
+        <v>4</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr"/>
+      <c r="AJ115" t="inlineStr"/>
+      <c r="AK115" t="inlineStr"/>
+      <c r="AL115" t="inlineStr"/>
+      <c r="AM115" t="inlineStr"/>
+      <c r="AN115" t="inlineStr"/>
+      <c r="AO115" t="inlineStr"/>
+      <c r="AP115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>MeetingMinutes</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Application that transcribes short meetings and produces a basic list of decisions and action items.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>4</v>
+      </c>
+      <c r="I116" t="n">
+        <v>2</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr"/>
+      <c r="AE116" t="inlineStr"/>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr"/>
+      <c r="AJ116" t="inlineStr"/>
+      <c r="AK116" t="inlineStr"/>
+      <c r="AL116" t="inlineStr"/>
+      <c r="AM116" t="inlineStr"/>
+      <c r="AN116" t="inlineStr"/>
+      <c r="AO116" t="inlineStr"/>
+      <c r="AP116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EmailPriority</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Email assistant that categorizes messages into high, medium, and low priority using simple text classification.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>3</v>
+      </c>
+      <c r="I117" t="n">
+        <v>2</v>
+      </c>
+      <c r="J117" t="n">
+        <v>2</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
+      <c r="AC117" t="inlineStr"/>
+      <c r="AD117" t="inlineStr"/>
+      <c r="AE117" t="inlineStr"/>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr"/>
+      <c r="AJ117" t="inlineStr"/>
+      <c r="AK117" t="inlineStr"/>
+      <c r="AL117" t="inlineStr"/>
+      <c r="AM117" t="inlineStr"/>
+      <c r="AN117" t="inlineStr"/>
+      <c r="AO117" t="inlineStr"/>
+      <c r="AP117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CampusEnergy</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>College dashboard that displays building electricity consumption and compares usage between departments.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Smart Campus</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H118" t="n">
+        <v>3</v>
+      </c>
+      <c r="I118" t="n">
+        <v>2</v>
+      </c>
+      <c r="J118" t="n">
+        <v>2</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="inlineStr"/>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="inlineStr"/>
+      <c r="AK118" t="inlineStr"/>
+      <c r="AL118" t="inlineStr"/>
+      <c r="AM118" t="inlineStr"/>
+      <c r="AN118" t="inlineStr"/>
+      <c r="AO118" t="inlineStr"/>
+      <c r="AP118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>LabEquipment Tracker</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Inventory system that records laboratory equipment, availability, maintenance dates, and current borrowers.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4</v>
+      </c>
+      <c r="I119" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr"/>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr"/>
+      <c r="AK119" t="inlineStr"/>
+      <c r="AL119" t="inlineStr"/>
+      <c r="AM119" t="inlineStr"/>
+      <c r="AN119" t="inlineStr"/>
+      <c r="AO119" t="inlineStr"/>
+      <c r="AP119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ExamSeating</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>College utility that automatically generates examination seating arrangements while avoiding duplicate department and roll-number conflicts.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>College Hackathon</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>4</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" t="n">
+        <v>2</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr"/>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="inlineStr"/>
+      <c r="AK120" t="inlineStr"/>
+      <c r="AL120" t="inlineStr"/>
+      <c r="AM120" t="inlineStr"/>
+      <c r="AN120" t="inlineStr"/>
+      <c r="AO120" t="inlineStr"/>
+      <c r="AP120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CampusFeedback AI</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Student-feedback platform that groups complaints and suggestions into themes and presents recurring issues on an administrator dashboard.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Smart Campus</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Devpost</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>3</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3</v>
+      </c>
+      <c r="J121" t="n">
+        <v>2</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr"/>
+      <c r="AC121" t="inlineStr"/>
+      <c r="AD121" t="inlineStr"/>
+      <c r="AE121" t="inlineStr"/>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr"/>
+      <c r="AJ121" t="inlineStr"/>
+      <c r="AK121" t="inlineStr"/>
+      <c r="AL121" t="inlineStr"/>
+      <c r="AM121" t="inlineStr"/>
+      <c r="AN121" t="inlineStr"/>
+      <c r="AO121" t="inlineStr"/>
+      <c r="AP121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
